--- a/ecovirBenin_fictive.xlsx
+++ b/ecovirBenin_fictive.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\EcoVirBénin\Agg\aggregation\Publication_clean\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\EcoVirBénin\Agg\aggregation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C86E2F02-1CD2-404C-A6A7-A5845F2DBFEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6CD6FF8-6C29-4E23-A3EE-0E7E780A5EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="283">
   <si>
     <t>study_id</t>
   </si>
@@ -298,9 +298,6 @@
     <t>BEN/CNHU/MED/3</t>
   </si>
   <si>
-    <t>BEN/CNHU/MED/4</t>
-  </si>
-  <si>
     <t>BEN/CNHU/MED/5</t>
   </si>
   <si>
@@ -865,34 +862,13 @@
     <t>16/03/2006</t>
   </si>
   <si>
-    <t>BEN/HZAC/PED/11</t>
-  </si>
-  <si>
     <t>08/08/2016</t>
   </si>
   <si>
     <t>13/07/2020</t>
   </si>
   <si>
-    <t>BEN/HZAC/URG/11</t>
-  </si>
-  <si>
-    <t>BEN/HZAC/URG/12</t>
-  </si>
-  <si>
-    <t>BEN/HZAC/URG/13</t>
-  </si>
-  <si>
-    <t>BEN/CNHU/MED/11</t>
-  </si>
-  <si>
-    <t>BEN/CNHU/PED/11</t>
-  </si>
-  <si>
-    <t>BEN/CNHU/PED/12</t>
-  </si>
-  <si>
-    <t>BEN/CNHU/PED/13</t>
+    <t>23/03/2027</t>
   </si>
 </sst>
 </file>
@@ -1311,13 +1287,13 @@
         <v>64</v>
       </c>
       <c r="D2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -1325,7 +1301,7 @@
         <v>64</v>
       </c>
       <c r="B3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -1338,10 +1314,10 @@
         <v>64</v>
       </c>
       <c r="C5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -1349,10 +1325,10 @@
         <v>11</v>
       </c>
       <c r="C6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -1360,10 +1336,10 @@
         <v>11</v>
       </c>
       <c r="D7" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="I7" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -1371,7 +1347,7 @@
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -1379,7 +1355,7 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -1387,37 +1363,37 @@
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D10" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -1425,37 +1401,37 @@
         <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D14" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G14" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>281</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -1463,37 +1439,37 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D18" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G18" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H18" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -1501,37 +1477,37 @@
         <v>15</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D22" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G22" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H22" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I22" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
@@ -1539,37 +1515,37 @@
         <v>16</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D26" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G26" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H26" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I26" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>284</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
@@ -1577,37 +1553,37 @@
         <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D30" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>284</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>285</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
@@ -1615,37 +1591,37 @@
         <v>18</v>
       </c>
       <c r="B34" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D34" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>284</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>285</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>286</v>
+        <v>18</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1653,37 +1629,37 @@
         <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D38" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="G38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H38" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I38" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
@@ -1691,37 +1667,37 @@
         <v>20</v>
       </c>
       <c r="B42" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D42" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H42" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I42" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
@@ -1729,37 +1705,37 @@
         <v>21</v>
       </c>
       <c r="B46" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G46" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H46" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
@@ -1767,37 +1743,37 @@
         <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D50" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G50" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H50" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I50" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
@@ -1805,37 +1781,37 @@
         <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D54" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H54" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I54" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
@@ -1843,37 +1819,37 @@
         <v>24</v>
       </c>
       <c r="B58" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C58" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D58" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G58" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H58" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I58" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
@@ -1881,37 +1857,37 @@
         <v>42</v>
       </c>
       <c r="B62" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D62" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="G62" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H62" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I62" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
@@ -1919,22 +1895,22 @@
         <v>43</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C66" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D66" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="G66" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H66" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I66" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
@@ -1942,22 +1918,22 @@
         <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D67" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G67" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H67" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I67" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
@@ -1965,22 +1941,22 @@
         <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D68" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="G68" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H68" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I68" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
@@ -1988,22 +1964,22 @@
         <v>29</v>
       </c>
       <c r="B69" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D69" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="G69" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H69" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I69" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
@@ -2011,22 +1987,22 @@
         <v>30</v>
       </c>
       <c r="B70" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C70" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D70" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G70" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H70" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I70" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
@@ -2034,22 +2010,22 @@
         <v>31</v>
       </c>
       <c r="B71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D71" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="G71" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H71" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I71" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
@@ -2057,22 +2033,22 @@
         <v>32</v>
       </c>
       <c r="B72" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D72" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G72" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H72" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I72" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
@@ -2080,22 +2056,22 @@
         <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D73" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="G73" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H73" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I73" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
@@ -2103,22 +2079,22 @@
         <v>34</v>
       </c>
       <c r="B74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D74" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="G74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H74" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I74" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
@@ -2126,22 +2102,22 @@
         <v>35</v>
       </c>
       <c r="B75" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C75" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D75" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="G75" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H75" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I75" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
@@ -2149,22 +2125,22 @@
         <v>36</v>
       </c>
       <c r="B76" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C76" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D76" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G76" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H76" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I76" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
@@ -2172,22 +2148,22 @@
         <v>37</v>
       </c>
       <c r="B77" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C77" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D77" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="G77" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H77" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I77" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
@@ -2195,22 +2171,22 @@
         <v>38</v>
       </c>
       <c r="B78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D78" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G78" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H78" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I78" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
@@ -2218,22 +2194,22 @@
         <v>39</v>
       </c>
       <c r="B79" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D79" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G79" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H79" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I79" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
@@ -2241,22 +2217,22 @@
         <v>40</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C80" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D80" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="G80" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H80" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I80" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
@@ -2264,22 +2240,22 @@
         <v>41</v>
       </c>
       <c r="B81" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C81" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D81" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G81" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H81" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I81" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
@@ -2287,22 +2263,22 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C82" t="s">
+        <v>184</v>
+      </c>
+      <c r="D82" t="s">
         <v>185</v>
       </c>
-      <c r="D82" t="s">
-        <v>186</v>
-      </c>
       <c r="G82" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H82" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I82" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
@@ -2310,22 +2286,22 @@
         <v>53</v>
       </c>
       <c r="B83" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C83" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D83" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G83" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H83" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I83" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
@@ -2333,22 +2309,22 @@
         <v>44</v>
       </c>
       <c r="B84" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C84" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D84" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G84" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H84" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I84" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
@@ -2356,22 +2332,22 @@
         <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C85" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D85" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="G85" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H85" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I85" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
@@ -2379,22 +2355,22 @@
         <v>46</v>
       </c>
       <c r="B86" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C86" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D86" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G86" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H86" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I86" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
@@ -2402,22 +2378,22 @@
         <v>47</v>
       </c>
       <c r="B87" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C87" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D87" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="G87" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H87" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I87" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
@@ -2425,22 +2401,22 @@
         <v>48</v>
       </c>
       <c r="B88" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D88" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="G88" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H88" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I88" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
@@ -2448,22 +2424,22 @@
         <v>49</v>
       </c>
       <c r="B89" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C89" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D89" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G89" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H89" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I89" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
@@ -2471,22 +2447,22 @@
         <v>50</v>
       </c>
       <c r="B90" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D90" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G90" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H90" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I90" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
@@ -2494,22 +2470,22 @@
         <v>51</v>
       </c>
       <c r="B91" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D91" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G91" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H91" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I91" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
@@ -2517,22 +2493,22 @@
         <v>52</v>
       </c>
       <c r="B92" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C92" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D92" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G92" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H92" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I92" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
@@ -2540,22 +2516,22 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C93" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D93" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G93" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H93" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I93" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
@@ -2563,22 +2539,22 @@
         <v>54</v>
       </c>
       <c r="B94" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C94" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D94" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G94" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H94" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I94" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
@@ -2586,22 +2562,22 @@
         <v>55</v>
       </c>
       <c r="B95" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C95" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D95" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G95" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H95" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I95" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
@@ -2609,22 +2585,22 @@
         <v>56</v>
       </c>
       <c r="B96" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C96" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D96" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G96" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H96" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I96" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
@@ -2632,22 +2608,22 @@
         <v>57</v>
       </c>
       <c r="B97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C97" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D97" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G97" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H97" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I97" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
@@ -2655,22 +2631,22 @@
         <v>58</v>
       </c>
       <c r="B98" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C98" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D98" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G98" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H98" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I98" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
@@ -2678,22 +2654,22 @@
         <v>59</v>
       </c>
       <c r="B99" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C99" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D99" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G99" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H99" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I99" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
@@ -2701,22 +2677,22 @@
         <v>60</v>
       </c>
       <c r="B100" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C100" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D100" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G100" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H100" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I100" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
@@ -2724,22 +2700,22 @@
         <v>61</v>
       </c>
       <c r="B101" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C101" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D101" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G101" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H101" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I101" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
@@ -2747,22 +2723,22 @@
         <v>62</v>
       </c>
       <c r="B102" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C102" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D102" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G102" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H102" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I102" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
@@ -2770,22 +2746,22 @@
         <v>75</v>
       </c>
       <c r="B103" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C103" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D103" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G103" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H103" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I103" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
@@ -2793,22 +2769,22 @@
         <v>86</v>
       </c>
       <c r="B104" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C104" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D104" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="G104" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H104" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I104" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
@@ -2816,22 +2792,22 @@
         <v>65</v>
       </c>
       <c r="B105" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C105" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D105" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G105" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H105" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I105" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
@@ -2839,22 +2815,22 @@
         <v>66</v>
       </c>
       <c r="B106" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C106" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D106" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G106" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H106" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I106" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
@@ -2862,22 +2838,22 @@
         <v>67</v>
       </c>
       <c r="B107" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D107" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G107" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H107" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I107" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
@@ -2885,22 +2861,22 @@
         <v>68</v>
       </c>
       <c r="B108" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D108" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G108" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H108" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I108" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
@@ -2908,22 +2884,22 @@
         <v>69</v>
       </c>
       <c r="B109" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C109" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D109" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G109" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H109" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I109" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
@@ -2931,22 +2907,22 @@
         <v>70</v>
       </c>
       <c r="B110" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C110" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D110" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G110" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H110" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I110" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
@@ -2954,22 +2930,22 @@
         <v>71</v>
       </c>
       <c r="B111" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C111" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D111" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G111" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H111" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I111" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
@@ -2977,22 +2953,22 @@
         <v>72</v>
       </c>
       <c r="B112" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C112" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D112" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G112" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H112" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I112" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
@@ -3000,22 +2976,22 @@
         <v>73</v>
       </c>
       <c r="B113" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C113" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D113" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G113" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H113" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I113" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
@@ -3023,45 +2999,45 @@
         <v>74</v>
       </c>
       <c r="B114" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D114" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G114" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H114" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I114" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B115" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C115" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D115" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G115" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H115" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I115" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
@@ -3069,22 +3045,22 @@
         <v>76</v>
       </c>
       <c r="B116" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C116" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D116" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="G116" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H116" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I116" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
@@ -3092,22 +3068,22 @@
         <v>77</v>
       </c>
       <c r="B117" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C117" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D117" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G117" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H117" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I117" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
@@ -3115,22 +3091,22 @@
         <v>78</v>
       </c>
       <c r="B118" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C118" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D118" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="G118" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H118" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I118" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
@@ -3138,22 +3114,22 @@
         <v>79</v>
       </c>
       <c r="B119" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C119" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D119" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G119" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H119" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I119" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
@@ -3161,37 +3137,37 @@
         <v>10</v>
       </c>
       <c r="B120" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C120" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D120" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G120" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H120" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I120" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
@@ -3199,37 +3175,37 @@
         <v>81</v>
       </c>
       <c r="B124" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C124" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D124" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G124" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H124" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I124" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
@@ -3237,37 +3213,37 @@
         <v>82</v>
       </c>
       <c r="B128" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C128" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D128" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="G128" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H128" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I128" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
@@ -3275,75 +3251,75 @@
         <v>83</v>
       </c>
       <c r="B132" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C132" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D132" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="G132" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H132" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I132" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B136" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C136" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D136" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G136" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H136" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I136" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>287</v>
+        <v>95</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
@@ -3351,37 +3327,37 @@
         <v>85</v>
       </c>
       <c r="B140" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C140" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D140" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G140" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H140" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I140" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
@@ -3389,37 +3365,37 @@
         <v>13</v>
       </c>
       <c r="B144" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C144" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D144" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G144" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H144" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I144" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
@@ -3427,37 +3403,37 @@
         <v>87</v>
       </c>
       <c r="B148" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C148" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D148" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G148" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H148" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I148" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>288</v>
+        <v>87</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>289</v>
+        <v>87</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
@@ -3465,37 +3441,37 @@
         <v>88</v>
       </c>
       <c r="B152" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C152" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D152" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G152" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H152" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I152" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>288</v>
+        <v>88</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>289</v>
+        <v>88</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>290</v>
+        <v>88</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
@@ -3503,22 +3479,22 @@
         <v>12</v>
       </c>
       <c r="B156" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C156" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D156" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G156" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H156" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I156" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
@@ -3526,37 +3502,37 @@
         <v>90</v>
       </c>
       <c r="B157" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C157" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D157" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G157" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H157" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I157" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
@@ -3564,22 +3540,22 @@
         <v>63</v>
       </c>
       <c r="B161" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C161" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D161" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G161" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H161" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I161" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
@@ -3587,98 +3563,98 @@
         <v>80</v>
       </c>
       <c r="B162" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C162" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D162" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G162" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H162" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I162" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B166" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C166" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D166" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="G166" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H166" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I166" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B170" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C170" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D170" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G170" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H170" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I170" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
@@ -3686,37 +3662,37 @@
         <v>84</v>
       </c>
       <c r="B171" t="s">
-        <v>172</v>
-      </c>
-      <c r="C171" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="D171" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G171" t="s">
-        <v>185</v>
-      </c>
-      <c r="H171" t="s">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="I171" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>86</v>
+        <v>84</v>
+      </c>
+      <c r="H173" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>87</v>
+        <v>84</v>
+      </c>
+      <c r="C174" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
@@ -3724,83 +3700,83 @@
         <v>89</v>
       </c>
       <c r="B175" t="s">
-        <v>176</v>
-      </c>
-      <c r="C175" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="D175" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G175" t="s">
-        <v>185</v>
-      </c>
-      <c r="H175" t="s">
-        <v>274</v>
+        <v>184</v>
       </c>
       <c r="I175" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="C176" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>91</v>
+        <v>89</v>
+      </c>
+      <c r="H177" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B179" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C179" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D179" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G179" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H179" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="I179" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B180" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C180" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D180" t="s">
+        <v>271</v>
+      </c>
+      <c r="G180" t="s">
+        <v>184</v>
+      </c>
+      <c r="H180" t="s">
         <v>272</v>
       </c>
-      <c r="G180" t="s">
-        <v>185</v>
-      </c>
-      <c r="H180" t="s">
-        <v>273</v>
-      </c>
       <c r="I180" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
